--- a/output/pdf_financials_xlsx/PNRG.xlsx
+++ b/output/pdf_financials_xlsx/PNRG.xlsx
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.942673</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.564793</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.237893</v>
       </c>
     </row>
     <row r="93">
@@ -2331,13 +2331,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>2.946</v>
+        <v>2.796065</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>8.895141000000001</v>
+        <v>3.624608</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.4</v>
+        <v>-1.032761</v>
       </c>
     </row>
     <row r="119">
@@ -3017,7 +3017,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3351,7 +3355,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>1.942673</v>
       </c>
@@ -3804,7 +3812,11 @@
           <t>Exploration and evaluation expenditures (Note 6)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>-0.149935</v>
       </c>

--- a/output/pdf_financials_xlsx/PNRG.xlsx
+++ b/output/pdf_financials_xlsx/PNRG.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.032342</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.078376</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.028639</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.255238</v>
+        <v>-7.28758</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.520028</v>
+        <v>-5.598404</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-16.055664</v>
+        <v>-16.084303</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.255238</v>
+        <v>-7.28758</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.520028</v>
+        <v>-5.598404</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-16.055664</v>
+        <v>-16.084303</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4.6748</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.077996</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.258976</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>4.6748</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.077996</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.258976</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>5.477524</v>
+        <v>0.802724</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.095821</v>
+        <v>0.017825</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.267672</v>
+        <v>0.008696000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
